--- a/data/update_history.xlsx
+++ b/data/update_history.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R1363f8bf8c104c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R63d28577a48444a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -24,8 +24,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF24282C"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -37,8 +42,18 @@
         <x:fgColor rgb="FF2F81F7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF288FE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F8FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="6">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
@@ -58,11 +73,33 @@
         <x:color rgb="FFD7E3EE"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFDCE3E6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFDCE3E6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFDCE3E6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFDCE3E6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFDCE3E6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFDCE3E6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -88,6 +125,24 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -302,21 +357,25 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="92" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="14" t="str">
         <x:v>Версія</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="14" t="str">
         <x:v>Опис оновлення</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="10"/>
-      <x:c r="B2" s="10"/>
+    <x:row r="2" ht="58" customHeight="1">
+      <x:c r="A2" s="17" t="str">
+        <x:v>1.0.0</x:v>
+      </x:c>
+      <x:c r="B2" s="18" t="str">
+        <x:v>Перший публічний реліз CoDA: каталог ДБН, локальні та імпортовані нотатки, обмін Archicad / Excel, оновлення бази й автоматична перевірка оновлень програми.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="11"/>
@@ -397,7 +456,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8629fe442f04964"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfe97f5a39574350"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/update_history.xlsx
+++ b/data/update_history.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R63d28577a48444a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R37c2cab9cf7f4a4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -377,9 +377,13 @@
         <x:v>Перший публічний реліз CoDA: каталог ДБН, локальні та імпортовані нотатки, обмін Archicad / Excel, оновлення бази й автоматична перевірка оновлень програми.</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="11"/>
-      <x:c r="B3" s="11"/>
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="11" t="str">
+        <x:v>1.1.0</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>Пошук у PDF, кольорові текстові закладки та точне виділення тексту на масштабах 50–300%; резервне копіювання і повне відновлення даних користувача через .codasaves; у закріплених ДБН показуються номер і назва документа.</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="11"/>
@@ -456,7 +460,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfe97f5a39574350"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51517b8346f949fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/update_history.xlsx
+++ b/data/update_history.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R37c2cab9cf7f4a4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R29a95c1d05c349ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateHistoryTable" displayName="UpdateHistoryTable" ref="A1:B21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateHistoryTable" displayName="UpdateHistoryTable" ref="A1:B22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Версія"/>
     <x:tableColumn id="2" name="Опис оновлення"/>
@@ -386,8 +386,12 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="11"/>
-      <x:c r="B4" s="11"/>
+      <x:c r="A4" s="11" t="str">
+        <x:v>1.1.1</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Текстові закладки тепер можна створювати з виділення на кількох сторінках PDF; виправлено вирівнювання кнопки видалення закладки, відображення опису оновлення програми та повідомлень про помилки оновлення бази ДБН.</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
       <x:c r="A5" s="11"/>
@@ -457,10 +461,18 @@
       <x:c r="A21" s="12"/>
       <x:c r="B21" s="12"/>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>1.1.1</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Текстові закладки тепер можна створювати з виділення на кількох сторінках PDF; виправлено вирівнювання кнопки видалення закладки, відображення опису оновлення програми та повідомлень про помилки оновлення бази ДБН.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51517b8346f949fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8859003282347b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/update_history.xlsx
+++ b/data/update_history.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R85cd60db39cd4546"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R68d7a06fe3a4452b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -104,7 +104,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -126,6 +126,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -392,10 +395,18 @@
         <x:v>Добавлено можливість редагування вже сформованих документів в ЄДЕССБ</x:v>
       </x:c>
     </x:row>
+    <x:row r="7" ht="60" customHeight="1">
+      <x:c r="A7" s="8" t="str">
+        <x:v>1.2.2</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>Добавлено відображення результатів пошуку у бічному вікні. Візуальні зміни відображення каталогу Державних будівельних норм</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3e753813aa04403"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17356450aff14d18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/update_history.xlsx
+++ b/data/update_history.xlsx
@@ -2,44 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R68d7a06fe3a4452b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R3b0be6e26e4d4fbb"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">Версія</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Опис оновлення</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1.0.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Перший публічний реліз CoDA: каталог ДБН, локальні та імпортовані нотатки, обмін Archicad / Excel ( в розробці), оновлення бази й автоматична перевірка оновлень програми.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1.1.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Реалізовано пошук у PDF і кольорові текстові закладки. Резервне копіювання і повне відновлення даних користувача. Виправлення помилок.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1.1.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Виправлення помилок у роботі текстових закладок. Виправлення технічних помилок.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1.2.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Додано розділ «ЄДЕССБ». Додано розділ «Будівельні матеріали». Розділено імпорт і експорт даних користувача за категоріями. Виправлено помилок.</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -139,7 +108,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateHistory" displayName="UpdateHistory" ref="A1:B4" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateHistoryTable" displayName="UpdateHistoryTable" ref="A1:B8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Версія"/>
     <x:tableColumn id="2" name="Опис оновлення"/>
@@ -348,43 +317,43 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.350000381469727" customHeight="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
+      <x:c r="A1" s="1" t="str">
+        <x:v>Версія</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>Опис оновлення</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="57.599998474121094" customHeight="1">
-      <x:c r="A2" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="A2" s="3" t="str">
+        <x:v>1.0.0</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="str">
+        <x:v>Перший публічний реліз CoDA: каталог ДБН, локальні та імпортовані нотатки, обмін Archicad / Excel ( в розробці), оновлення бази й автоматична перевірка оновлень програми.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="57.599998474121094" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>5</x:v>
+      <x:c r="A3" s="2" t="str">
+        <x:v>1.1.0</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>Реалізовано пошук у PDF і кольорові текстові закладки. Резервне копіювання і повне відновлення даних користувача. Виправлення помилок.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="57.599998474121094" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>7</x:v>
+      <x:c r="A4" s="3" t="str">
+        <x:v>1.1.1</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="str">
+        <x:v>Виправлення помилок у роботі текстових закладок. Виправлення технічних помилок.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="168" customHeight="1">
-      <x:c r="A5" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>9</x:v>
+      <x:c r="A5" s="4" t="str">
+        <x:v>1.2.0</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="str">
+        <x:v>Додано розділ «ЄДЕССБ». Додано розділ «Будівельні матеріали». Розділено імпорт і експорт даних користувача за категоріями. Виправлено помилок.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
@@ -395,18 +364,26 @@
         <x:v>Добавлено можливість редагування вже сформованих документів в ЄДЕССБ</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="60" customHeight="1">
+    <x:row r="7" ht="13.800000190734863" hidden="0" customHeight="1">
       <x:c r="A7" s="8" t="str">
         <x:v>1.2.2</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
         <x:v>Добавлено відображення результатів пошуку у бічному вікні. Візуальні зміни відображення каталогу Державних будівельних норм</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="13.800000190734863" hidden="0" customHeight="1">
+      <x:c r="A8" s="8" t="str">
+        <x:v>1.3.0</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>Видалено функціонал нотаток. Добавлено функціонал "Бібліотека"</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17356450aff14d18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb982ee5fe0314dd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/update_history.xlsx
+++ b/data/update_history.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R3b0be6e26e4d4fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="Rf51a67ec755b4d64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,6 +32,17 @@
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Arial"/>
     </x:font>
   </x:fonts>
   <x:fills count="4">
@@ -73,7 +84,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -98,6 +109,31 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -108,7 +144,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateHistoryTable" displayName="UpdateHistoryTable" ref="A1:B8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateHistoryTable" displayName="UpdateHistoryTable" ref="A1:B9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Версія"/>
     <x:tableColumn id="2" name="Опис оновлення"/>
@@ -312,78 +348,86 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="13.800000190734863"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" customWidth="1"/>
-    <x:col min="2" max="2" width="110" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="118" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="22.350000381469727" customHeight="1">
-      <x:c r="A1" s="1" t="str">
+    <x:row r="1" ht="13.800000190734863" hidden="0" customHeight="1">
+      <x:c r="A1" s="17" t="str">
         <x:v>Версія</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="str">
+      <x:c r="B1" s="17" t="str">
         <x:v>Опис оновлення</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="57.599998474121094" customHeight="1">
-      <x:c r="A2" s="3" t="str">
+    <x:row r="2" ht="24" hidden="0" customHeight="1">
+      <x:c r="A2" s="10" t="str">
         <x:v>1.0.0</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="10" t="str">
         <x:v>Перший публічний реліз CoDA: каталог ДБН, локальні та імпортовані нотатки, обмін Archicad / Excel ( в розробці), оновлення бази й автоматична перевірка оновлень програми.</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="57.599998474121094" customHeight="1">
-      <x:c r="A3" s="2" t="str">
+    <x:row r="3" ht="13.800000190734863" hidden="0" customHeight="1">
+      <x:c r="A3" s="11" t="str">
         <x:v>1.1.0</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="str">
+      <x:c r="B3" s="11" t="str">
         <x:v>Реалізовано пошук у PDF і кольорові текстові закладки. Резервне копіювання і повне відновлення даних користувача. Виправлення помилок.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="57.599998474121094" customHeight="1">
-      <x:c r="A4" s="3" t="str">
+    <x:row r="4" ht="13.800000190734863" hidden="0" customHeight="1">
+      <x:c r="A4" s="10" t="str">
         <x:v>1.1.1</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>Виправлення помилок у роботі текстових закладок. Виправлення технічних помилок.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="168" customHeight="1">
-      <x:c r="A5" s="4" t="str">
+    <x:row r="5" ht="13.800000190734863" hidden="0" customHeight="1">
+      <x:c r="A5" s="13" t="str">
         <x:v>1.2.0</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="13" t="str">
         <x:v>Додано розділ «ЄДЕССБ». Додано розділ «Будівельні матеріали». Розділено імпорт і експорт даних користувача за категоріями. Виправлено помилок.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="6" t="str">
+    <x:row r="6" ht="13.800000190734863" hidden="0" customHeight="1">
+      <x:c r="A6" s="13" t="str">
         <x:v>1.2.1</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="str">
+      <x:c r="B6" s="13" t="str">
         <x:v>Добавлено можливість редагування вже сформованих документів в ЄДЕССБ</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="13.800000190734863" hidden="0" customHeight="1">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="13" t="str">
         <x:v>1.2.2</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="13" t="str">
         <x:v>Добавлено відображення результатів пошуку у бічному вікні. Візуальні зміни відображення каталогу Державних будівельних норм</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="13.800000190734863" hidden="0" customHeight="1">
-      <x:c r="A8" s="8" t="str">
+      <x:c r="A8" s="13" t="str">
         <x:v>1.3.0</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
+      <x:c r="B8" s="13" t="str">
         <x:v>Видалено функціонал нотаток. Добавлено функціонал "Бібліотека"</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
+      <x:c r="A9" s="13" t="str">
+        <x:v>1.3.1</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="str">
+        <x:v>Додано вбудований каталог PDF-інструкцій з роботи в ЄДЕССБ. Інструкції відкриваються у внутрішньому переглядачі CoDA та оновлюються разом із програмою.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb982ee5fe0314dd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb58effccae7848c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/update_history.xlsx
+++ b/data/update_history.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="Rf51a67ec755b4d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R82dc11d02f86496f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -416,18 +416,18 @@
         <x:v>Видалено функціонал нотаток. Добавлено функціонал "Бібліотека"</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="24" hidden="0" customHeight="1">
+    <x:row r="9" ht="36" hidden="0" customHeight="1">
       <x:c r="A9" s="13" t="str">
         <x:v>1.3.1</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
-        <x:v>Додано вбудований каталог PDF-інструкцій з роботи в ЄДЕССБ. Інструкції відкриваються у внутрішньому переглядачі CoDA та оновлюються разом із програмою.</x:v>
+        <x:v>Додано вбудований каталог PDF-інструкцій з роботи в ЄДЕССБ. Інструкції відкриваються у внутрішньому переглядачі CoDA та оновлюються разом із програмою. Додано можливість додавати інструкції до обраних: обрані інструкції відображаються першими у каталозі та зберігаються в даних користувача.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb58effccae7848c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R939c9feb83c449ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/update_history.xlsx
+++ b/data/update_history.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R82dc11d02f86496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Історія оновлень" sheetId="1" r:id="R5832132b963b4fd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -424,10 +424,20 @@
         <x:v>Додано вбудований каталог PDF-інструкцій з роботи в ЄДЕССБ. Інструкції відкриваються у внутрішньому переглядачі CoDA та оновлюються разом із програмою. Додано можливість додавати інструкції до обраних: обрані інструкції відображаються першими у каталозі та зберігаються в даних користувача.</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="60" customHeight="1">
+      <x:c r="A10" s="13" t="str">
+        <x:v>1.3.2</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="str">
+        <x:v>1. Добавлено можливість редагувати назву проєкту у функціоналі ЄДЕССБ
+2. Змінено відображення переліку проєктів у функціоналі ЄДЕССБ
+3. Змінено відображення бази документів ЄДЕССБ</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R939c9feb83c449ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8361cf2c26a94f9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>